--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -678,6 +678,68 @@
         </is>
       </c>
       <c r="L4" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OPENCODE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>space-bunny-free</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>16793</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22682</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1320.5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>toplam_metin=1;makro=1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>hayir</t>
         </is>
@@ -738,16 +800,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>16793</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>22682</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -740,6 +740,64 @@
         </is>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>hayir</t>
         </is>
@@ -819,7 +877,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -740,64 +740,6 @@
         </is>
       </c>
       <c r="L5" t="inlineStr">
-        <is>
-          <t>hayir</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>gunluk</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
         <is>
           <t>hayir</t>
         </is>
@@ -877,7 +819,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -433,6 +433,7 @@
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -496,6 +497,11 @@
           <t>rozet</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>yazan_dagilimi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,6 +564,7 @@
           <t>hayir</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -620,6 +627,7 @@
           <t>hayir</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -682,6 +690,7 @@
           <t>hayir</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -742,6 +751,70 @@
       <c r="L5" t="inlineStr">
         <is>
           <t>hayir</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>karisik (4 model, 11 bolum)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ZAI/glm-5.3-flash x3, AMD/DeepSeek-V4-Flash x5, NVID/glm-5.3 x2, OR/nemotron x2, YEDEK/gpt-oss-120b x1</t>
         </is>
       </c>
     </row>
@@ -819,7 +892,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -434,6 +434,8 @@
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,6 +504,16 @@
           <t>yazan_dagilimi</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>kosu_token_in</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>kosu_token_out</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -565,6 +577,16 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -628,6 +650,16 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -691,6 +723,16 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -754,6 +796,16 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -815,6 +867,16 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>ZAI/glm-5.3-flash x3, AMD/DeepSeek-V4-Flash x5, NVID/glm-5.3 x2, OR/nemotron x2, YEDEK/gpt-oss-120b x1</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -877,6 +877,83 @@
       <c r="O6" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>16393</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9707</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1621.7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>toplam_metin=1;faiz=1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>16393</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>9707</t>
         </is>
       </c>
     </row>
@@ -935,16 +1012,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>16793</v>
+        <v>33186</v>
       </c>
       <c r="D2" t="n">
-        <v>22682</v>
+        <v>32389</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -954,6 +954,83 @@
       <c r="O7" t="inlineStr">
         <is>
           <t>9707</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>makro</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>10827</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>11586</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>727.9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>toplam_metin=1;faiz=4;makro=5</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>10827</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>11586</t>
         </is>
       </c>
     </row>
@@ -1050,16 +1127,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>10827</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>11586</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1031,6 +1031,83 @@
       <c r="O8" t="inlineStr">
         <is>
           <t>11586</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>16532</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8967</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1543.5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>isim=3;toplam_metin=1;piyasa=1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>16532</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>8967</t>
         </is>
       </c>
     </row>
@@ -1089,16 +1166,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>33186</v>
+        <v>49718</v>
       </c>
       <c r="D2" t="n">
-        <v>32389</v>
+        <v>41356</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1108,6 +1108,83 @@
       <c r="O9" t="inlineStr">
         <is>
           <t>8967</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>16118</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>8694</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1508.1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>isim=2;toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>16118</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>8694</t>
         </is>
       </c>
     </row>
@@ -1166,16 +1243,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>49718</v>
+        <v>65836</v>
       </c>
       <c r="D2" t="n">
-        <v>41356</v>
+        <v>50050</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1185,6 +1185,83 @@
       <c r="O10" t="inlineStr">
         <is>
           <t>8694</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>AMD/DeepSeek-V4-Flashx6, ZAI/glm-5.3-flashx1, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>80072</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>18213</t>
         </is>
       </c>
     </row>
@@ -1262,16 +1339,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1912</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1333</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1262,6 +1262,83 @@
       <c r="O11" t="inlineStr">
         <is>
           <t>18213</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1944</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>AMD/DeepSeek-V4-Flashx7, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>81833</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>9303</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1416,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>1912</v>
+        <v>3856</v>
       </c>
       <c r="D3" t="n">
-        <v>1333</v>
+        <v>2380</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1339,6 +1339,83 @@
       <c r="O12" t="inlineStr">
         <is>
           <t>9303</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>makro</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DeepSeek-V4-Flash</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>11408</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2950</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>158.9</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>AMD/DeepSeek-V4-Flashx1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>11408</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2950</t>
         </is>
       </c>
     </row>
@@ -1435,16 +1512,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10827</v>
+        <v>22235</v>
       </c>
       <c r="D4" t="n">
-        <v>11586</v>
+        <v>14536</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1416,6 +1416,83 @@
       <c r="O13" t="inlineStr">
         <is>
           <t>2950</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>16260</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10451</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>883.1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>isim=1;toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>16260</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>10451</t>
         </is>
       </c>
     </row>
@@ -1474,16 +1551,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>65836</v>
+        <v>82096</v>
       </c>
       <c r="D2" t="n">
-        <v>50050</v>
+        <v>60501</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1493,6 +1493,83 @@
       <c r="O14" t="inlineStr">
         <is>
           <t>10451</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>AMD/DeepSeek-V4-Flashx7, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>81907</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>9743</t>
         </is>
       </c>
     </row>
@@ -1570,16 +1647,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>3856</v>
+        <v>5809</v>
       </c>
       <c r="D3" t="n">
-        <v>2380</v>
+        <v>3358</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1570,6 +1570,83 @@
       <c r="O15" t="inlineStr">
         <is>
           <t>9743</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>OLLAMA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>gpt-oss:120b</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>14403</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3943</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>608.9</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>toplam_metin=1;faiz=1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>OLLAMA/gpt-oss:120bx1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>14403</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>3943</t>
         </is>
       </c>
     </row>
@@ -1628,16 +1705,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>82096</v>
+        <v>96499</v>
       </c>
       <c r="D2" t="n">
-        <v>60501</v>
+        <v>64444</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1647,6 +1647,83 @@
       <c r="O16" t="inlineStr">
         <is>
           <t>3943</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>isim=2;toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>AMD/DeepSeek-V4-Flashx6, OR/nvidia/nemotron-3-ultra-550b-a55b:freex1, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>9794</t>
         </is>
       </c>
     </row>
@@ -1724,16 +1801,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>5809</v>
+        <v>7805</v>
       </c>
       <c r="D3" t="n">
-        <v>3358</v>
+        <v>4351</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1724,6 +1724,83 @@
       <c r="O17" t="inlineStr">
         <is>
           <t>9794</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>makro</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>10664</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>9663</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>642.7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>enflasyon=2;toplam_metin=1;makro=2;piyasa=2</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>10664</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>9663</t>
         </is>
       </c>
     </row>
@@ -1820,16 +1897,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>22235</v>
+        <v>32899</v>
       </c>
       <c r="D4" t="n">
-        <v>14536</v>
+        <v>24199</v>
       </c>
       <c r="E4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1801,6 +1801,83 @@
       <c r="O18" t="inlineStr">
         <is>
           <t>9663</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OLLAMA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>gpt-oss:120b</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>14303</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4930</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>637.2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>isim=3;toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>OLLAMA/gpt-oss:120bx1</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>14303</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>4930</t>
         </is>
       </c>
     </row>
@@ -1859,16 +1936,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>96499</v>
+        <v>110802</v>
       </c>
       <c r="D2" t="n">
-        <v>64444</v>
+        <v>69374</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1878,6 +1878,83 @@
       <c r="O19" t="inlineStr">
         <is>
           <t>4930</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2077</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>toplam_metin=1;makro=1</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>AMD/DeepSeek-V4-Flashx6, OR/nvidia/nemotron-3-ultra-550b-a55b:freex1, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>80209</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>11681</t>
         </is>
       </c>
     </row>
@@ -1955,16 +2032,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>7805</v>
+        <v>9882</v>
       </c>
       <c r="D3" t="n">
-        <v>4351</v>
+        <v>5542</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1955,6 +1955,83 @@
       <c r="O20" t="inlineStr">
         <is>
           <t>11681</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>16374</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>11218</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>995.9</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>enflasyon=1;toplam_metin=1;piyasa=2</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>16374</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>11218</t>
         </is>
       </c>
     </row>
@@ -2013,16 +2090,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>110802</v>
+        <v>127176</v>
       </c>
       <c r="D2" t="n">
-        <v>69374</v>
+        <v>80592</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2032,6 +2032,83 @@
       <c r="O21" t="inlineStr">
         <is>
           <t>11218</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>AMD/DeepSeek-V4-Flashx7, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>82223</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>10076</t>
         </is>
       </c>
     </row>
@@ -2109,16 +2186,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>9882</v>
+        <v>11851</v>
       </c>
       <c r="D3" t="n">
-        <v>5542</v>
+        <v>6510</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2109,6 +2109,79 @@
       <c r="O22" t="inlineStr">
         <is>
           <t>10076</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>makro</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ZAI</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>deepseek-v4-flash-0731</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>11355</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>22019</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>11355</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>22019</t>
         </is>
       </c>
     </row>
@@ -2205,16 +2278,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>32899</v>
+        <v>44254</v>
       </c>
       <c r="D4" t="n">
-        <v>24199</v>
+        <v>46218</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2182,6 +2182,83 @@
       <c r="O23" t="inlineStr">
         <is>
           <t>22019</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DISC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>deepseek-v4-flash-0731</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>16867</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>7857</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>isim=1;toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>DISC/deepseek-v4-flash-0731x1</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>16867</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>7857</t>
         </is>
       </c>
     </row>
@@ -2240,16 +2317,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>127176</v>
+        <v>144043</v>
       </c>
       <c r="D2" t="n">
-        <v>80592</v>
+        <v>88449</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2259,6 +2259,83 @@
       <c r="O24" t="inlineStr">
         <is>
           <t>7857</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>AMD/DeepSeek-V4-Flashx6, OR/nvidia/nemotron-3-ultra-550b-a55b:freex1, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>80466</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>10789</t>
         </is>
       </c>
     </row>
@@ -2336,16 +2413,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>11851</v>
+        <v>13865</v>
       </c>
       <c r="D3" t="n">
-        <v>6510</v>
+        <v>7572</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2336,6 +2336,83 @@
       <c r="O25" t="inlineStr">
         <is>
           <t>10789</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>makro</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>10663</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>11256</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>689.1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>enflasyon=4;faiz=5;makro=2</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>10663</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>11256</t>
         </is>
       </c>
     </row>
@@ -2432,16 +2509,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>44254</v>
+        <v>54917</v>
       </c>
       <c r="D4" t="n">
-        <v>46218</v>
+        <v>57474</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2413,6 +2413,83 @@
       <c r="O26" t="inlineStr">
         <is>
           <t>11256</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>16504</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>7438</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1453.3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>isim=4;toplam_metin=1;endeks=1;piyasa=1</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>16504</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>7438</t>
         </is>
       </c>
     </row>
@@ -2471,16 +2548,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>144043</v>
+        <v>160547</v>
       </c>
       <c r="D2" t="n">
-        <v>88449</v>
+        <v>95887</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2490,6 +2490,83 @@
       <c r="O27" t="inlineStr">
         <is>
           <t>7438</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2137</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>isim=1;toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>AMD/DeepSeek-V4-Flashx5, OR/nvidia/nemotron-3-ultra-550b-a55b:freex2, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>80904</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>13569</t>
         </is>
       </c>
     </row>
@@ -2567,16 +2644,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>13865</v>
+        <v>16002</v>
       </c>
       <c r="D3" t="n">
-        <v>7572</v>
+        <v>8576</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2567,6 +2567,83 @@
       <c r="O28" t="inlineStr">
         <is>
           <t>13569</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>16423</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>9123</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>548.7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>toplam_metin=1;piyasa=1</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>16423</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>9123</t>
         </is>
       </c>
     </row>
@@ -2625,16 +2702,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>160547</v>
+        <v>176970</v>
       </c>
       <c r="D2" t="n">
-        <v>95887</v>
+        <v>105010</v>
       </c>
       <c r="E2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2644,6 +2644,83 @@
       <c r="O29" t="inlineStr">
         <is>
           <t>9123</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2078</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>enflasyon=1;toplam_metin=1;endeks=2;faiz=1;makro=1;piyasa=1</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>AMD/DeepSeek-V4-Flashx6, OR/nvidia/nemotron-3-ultra-550b-a55b:freex1, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>79765</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>11110</t>
         </is>
       </c>
     </row>
@@ -2721,16 +2798,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>16002</v>
+        <v>18080</v>
       </c>
       <c r="D3" t="n">
-        <v>8576</v>
+        <v>9440</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2721,6 +2721,83 @@
       <c r="O30" t="inlineStr">
         <is>
           <t>11110</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>makro</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>10660</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>8552</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>449.8</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>enflasyon=3;toplam_metin=1;faiz=3;makro=3;piyasa=1</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>10660</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>8552</t>
         </is>
       </c>
     </row>
@@ -2817,16 +2894,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>54917</v>
+        <v>65577</v>
       </c>
       <c r="D4" t="n">
-        <v>57474</v>
+        <v>66026</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2798,6 +2798,83 @@
       <c r="O31" t="inlineStr">
         <is>
           <t>8552</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NVID</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>16347</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>8320</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>225.3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>toplam_metin=1;piyasa=1</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>NVID/nvidia/nemotron-3-ultra-550b-a55bx1</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>16347</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>8320</t>
         </is>
       </c>
     </row>
@@ -2856,16 +2933,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>176970</v>
+        <v>193317</v>
       </c>
       <c r="D2" t="n">
-        <v>105010</v>
+        <v>113330</v>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2875,6 +2875,83 @@
       <c r="O32" t="inlineStr">
         <is>
           <t>8320</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>isim=1;toplam_metin=1;makro=1</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>AMD/DeepSeek-V4-Flashx6, OR/nvidia/nemotron-3-ultra-550b-a55b:freex1, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>79606</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>10256</t>
         </is>
       </c>
     </row>
@@ -2952,16 +3029,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>18080</v>
+        <v>20101</v>
       </c>
       <c r="D3" t="n">
-        <v>9440</v>
+        <v>10289</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2952,6 +2952,83 @@
       <c r="O33" t="inlineStr">
         <is>
           <t>10256</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NVID</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>16524</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>8767</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>190.4</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>isim=8;toplam_metin=1;piyasa=2</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>NVID/nvidia/nemotron-3-ultra-550b-a55bx1</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>16524</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>8767</t>
         </is>
       </c>
     </row>
@@ -3010,16 +3087,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>193317</v>
+        <v>209841</v>
       </c>
       <c r="D2" t="n">
-        <v>113330</v>
+        <v>122097</v>
       </c>
       <c r="E2" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3029,6 +3029,83 @@
       <c r="O34" t="inlineStr">
         <is>
           <t>8767</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>toplam_metin=1;faiz=1;makro=1</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>AMD/DeepSeek-V4-Flashx5, ZAI/glm-5.3-flashx1, OR/nvidia/nemotron-3-ultra-550b-a55b:freex1, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>80194</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>9918</t>
         </is>
       </c>
     </row>
@@ -3106,16 +3183,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>20101</v>
+        <v>22226</v>
       </c>
       <c r="D3" t="n">
-        <v>10289</v>
+        <v>11325</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3106,6 +3106,83 @@
       <c r="O35" t="inlineStr">
         <is>
           <t>9918</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>makro</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>10660</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>10999</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1734.8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>enflasyon=3;toplam_metin=1;faiz=3;makro=2;piyasa=1</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>21320</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>19814</t>
         </is>
       </c>
     </row>
@@ -3202,16 +3279,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>65577</v>
+        <v>76237</v>
       </c>
       <c r="D4" t="n">
-        <v>66026</v>
+        <v>77025</v>
       </c>
       <c r="E4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3183,6 +3183,83 @@
       <c r="O36" t="inlineStr">
         <is>
           <t>19814</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>OLLAMA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>gpt-oss:120b</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>14633</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>5116</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1155.6</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>isim=4;toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>OLLAMA/gpt-oss:120bx1</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>14633</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>5116</t>
         </is>
       </c>
     </row>
@@ -3241,16 +3318,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>209841</v>
+        <v>224474</v>
       </c>
       <c r="D2" t="n">
-        <v>122097</v>
+        <v>127213</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3260,6 +3260,83 @@
       <c r="O37" t="inlineStr">
         <is>
           <t>5116</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>isim=2;toplam_metin=1;makro=1</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>AMD/DeepSeek-V4-Flashx5, OR/nvidia/nemotron-3-ultra-550b-a55b:freex2, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>79289</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>11215</t>
         </is>
       </c>
     </row>
@@ -3337,16 +3414,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>22226</v>
+        <v>24288</v>
       </c>
       <c r="D3" t="n">
-        <v>11325</v>
+        <v>12379</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3337,6 +3337,83 @@
       <c r="O38" t="inlineStr">
         <is>
           <t>11215</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>makro</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>10773</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6260</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>366.7</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>enflasyon=1;toplam_metin=1;faiz=1</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>10773</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>6260</t>
         </is>
       </c>
     </row>
@@ -3433,16 +3510,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>76237</v>
+        <v>87010</v>
       </c>
       <c r="D4" t="n">
-        <v>77025</v>
+        <v>83285</v>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3414,6 +3414,83 @@
       <c r="O39" t="inlineStr">
         <is>
           <t>6260</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NVID2</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>16709</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>7570</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>433.8</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>isim=2;toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>NVID2/nvidia/nemotron-3-ultra-550b-a55bx1</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>16709</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>7570</t>
         </is>
       </c>
     </row>
@@ -3472,16 +3549,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>224474</v>
+        <v>241183</v>
       </c>
       <c r="D2" t="n">
-        <v>127213</v>
+        <v>134783</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -3425,22 +3425,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>derin</t>
+          <t>makro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NVID2</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>nvidia/nemotron-3-ultra-550b-a55b</t>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3450,27 +3450,27 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>16709</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>433.8</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>isim=2;toplam_metin=1</t>
+          <t>enflasyon=4;faiz=4;makro=3</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3480,17 +3480,17 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>NVID2/nvidia/nemotron-3-ultra-550b-a55bx1</t>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>16709</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7531</t>
         </is>
       </c>
     </row>
@@ -3549,16 +3549,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>241183</v>
+        <v>224474</v>
       </c>
       <c r="D2" t="n">
-        <v>134783</v>
+        <v>127213</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -3587,16 +3587,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>87010</v>
+        <v>97681</v>
       </c>
       <c r="D4" t="n">
-        <v>83285</v>
+        <v>90816</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3491,6 +3491,83 @@
       <c r="O40" t="inlineStr">
         <is>
           <t>7531</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>makro</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>10671</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>12803</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>716.4</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>enflasyon=2;faiz=5;makro=5;piyasa=2</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>10671</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>12803</t>
         </is>
       </c>
     </row>
@@ -3587,16 +3664,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>97681</v>
+        <v>108352</v>
       </c>
       <c r="D4" t="n">
-        <v>90816</v>
+        <v>103619</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3568,6 +3568,83 @@
       <c r="O41" t="inlineStr">
         <is>
           <t>12803</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>ZAI/glm-5.3-flashx3, OR/nvidia/nemotron-3-ultra-550b-a55b:freex2, AMD/DeepSeek-V4-Flashx1, OLLAMA/gpt-oss:120bx1, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>76879</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>44210</t>
         </is>
       </c>
     </row>
@@ -3645,16 +3722,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>24288</v>
+        <v>26388</v>
       </c>
       <c r="D3" t="n">
-        <v>12379</v>
+        <v>13630</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3645,6 +3645,83 @@
       <c r="O42" t="inlineStr">
         <is>
           <t>44210</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NVID2</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>16777</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>7986</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>369.5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>isim=2;toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>NVID2/nvidia/nemotron-3-ultra-550b-a55bx1</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>33554</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>16551</t>
         </is>
       </c>
     </row>
@@ -3703,16 +3780,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>224474</v>
+        <v>241251</v>
       </c>
       <c r="D2" t="n">
-        <v>127213</v>
+        <v>135199</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3722,6 +3722,83 @@
       <c r="O43" t="inlineStr">
         <is>
           <t>16551</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>23:18</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2085</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>ZAI/glm-5.3-flashx5, OLLAMA/gpt-oss:120bx2, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>74938</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>60976</t>
         </is>
       </c>
     </row>
@@ -3799,16 +3876,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>26388</v>
+        <v>28473</v>
       </c>
       <c r="D3" t="n">
-        <v>13630</v>
+        <v>14724</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3799,6 +3799,83 @@
       <c r="O44" t="inlineStr">
         <is>
           <t>60976</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>02:25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2079</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>toplam_metin=1;makro=1</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>ZAI/glm-5.3-flashx4, AMD/DeepSeek-V4-Flashx2, OLLAMA/gpt-oss:120bx1, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>74756</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>44331</t>
         </is>
       </c>
     </row>
@@ -3876,16 +3953,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>28473</v>
+        <v>30552</v>
       </c>
       <c r="D3" t="n">
-        <v>14724</v>
+        <v>15718</v>
       </c>
       <c r="E3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3876,6 +3876,83 @@
       <c r="O45" t="inlineStr">
         <is>
           <t>44331</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>makro</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>10665</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>11576</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>538.1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>enflasyon=10;faiz=10;makro=2;piyasa=3</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>10665</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>11576</t>
         </is>
       </c>
     </row>
@@ -3972,16 +4049,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>108352</v>
+        <v>119017</v>
       </c>
       <c r="D4" t="n">
-        <v>103619</v>
+        <v>115195</v>
       </c>
       <c r="E4" t="n">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3953,6 +3953,83 @@
       <c r="O46" t="inlineStr">
         <is>
           <t>11576</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NVID</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>16679</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>8265</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>231.5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>isim=1;toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>NVID/nvidia/nemotron-3-ultra-550b-a55bx1</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>16679</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>8265</t>
         </is>
       </c>
     </row>
@@ -4011,16 +4088,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>241251</v>
+        <v>257930</v>
       </c>
       <c r="D2" t="n">
-        <v>135199</v>
+        <v>143464</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4030,6 +4030,83 @@
       <c r="O47" t="inlineStr">
         <is>
           <t>8265</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>isim=2;toplam_metin=1;endeks=2</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex4, AMD/DeepSeek-V4-Flashx3, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>81854</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>18627</t>
         </is>
       </c>
     </row>
@@ -4107,16 +4184,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>30552</v>
+        <v>32587</v>
       </c>
       <c r="D3" t="n">
-        <v>15718</v>
+        <v>16653</v>
       </c>
       <c r="E3" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4107,6 +4107,83 @@
       <c r="O48" t="inlineStr">
         <is>
           <t>18627</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>OLLAMA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>gpt-oss:120b</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>14511</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>960.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>isim=1;toplam_metin=1;faiz=1;piyasa=1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>OLLAMA/gpt-oss:120bx1</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>14511</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>4203</t>
         </is>
       </c>
     </row>
@@ -4165,16 +4242,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>257930</v>
+        <v>272441</v>
       </c>
       <c r="D2" t="n">
-        <v>143464</v>
+        <v>147667</v>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4184,6 +4184,83 @@
       <c r="O49" t="inlineStr">
         <is>
           <t>4203</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>gunluk</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>YEDEK</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1720</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>isim=2;toplam_metin=1;makro=1</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>AMD/DeepSeek-V4-Flashx5, OR/nvidia/nemotron-3-ultra-550b-a55b:freex2, YEDEK/openai/gpt-oss-120bx1</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>80342</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>14321</t>
         </is>
       </c>
     </row>
@@ -4261,16 +4338,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>32587</v>
+        <v>34614</v>
       </c>
       <c r="D3" t="n">
-        <v>16653</v>
+        <v>18373</v>
       </c>
       <c r="E3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4261,6 +4261,83 @@
       <c r="O50" t="inlineStr">
         <is>
           <t>14321</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>derin</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>OLLAMA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>gpt-oss:120b</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>14685</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>4045</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>707.4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>enflasyon=1;toplam_metin=1</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>OLLAMA/gpt-oss:120bx1</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>14685</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>4045</t>
         </is>
       </c>
     </row>
@@ -4319,16 +4396,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>272441</v>
+        <v>287126</v>
       </c>
       <c r="D2" t="n">
-        <v>147667</v>
+        <v>151712</v>
       </c>
       <c r="E2" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">

--- a/data/kullanim-defteri.xlsx
+++ b/data/kullanim-defteri.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4338,6 +4338,83 @@
       <c r="O51" t="inlineStr">
         <is>
           <t>4045</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>makro</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-ultra-550b-a55b:free</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>10707</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>12260</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>326.7</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>enflasyon=3;toplam_metin=1;endeks=1;faiz=2;makro=3</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hayir</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>OR/nvidia/nemotron-3-ultra-550b-a55b:freex1</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>10707</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>12260</t>
         </is>
       </c>
     </row>
@@ -4434,16 +4511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>119017</v>
+        <v>129724</v>
       </c>
       <c r="D4" t="n">
-        <v>115195</v>
+        <v>127455</v>
       </c>
       <c r="E4" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
